--- a/Gruppenkasse2026.xlsx
+++ b/Gruppenkasse2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\OneDrive\Dokumente\Aammon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C0A20E4-4AEA-4D0B-88D6-8133CBD6A485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46753E6-59E9-4AF2-B07F-8CF6FDA3AA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2680" yWindow="3840" windowWidth="19200" windowHeight="11170" xr2:uid="{7FF8DE2F-8395-4BBB-B9AA-6DFC00115A33}"/>
   </bookViews>
@@ -33,6 +33,14 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>Updated</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +410,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E204165A-3358-4A12-A311-594C69261D29}">
-  <dimension ref="A1"/>
+  <dimension ref="E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <sheetData>
+    <row r="6" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>